--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.82.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.82.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.82.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.82.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="39" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.82.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.82.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0082.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0082.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: defendant is â€œunreasonablyâ€� delayed. It has been also</t>
+          <t>L7: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW :: The words are " in every other case → that is, in every</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L36: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: The words are " in every other case"â€”that is, in every â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]SPEEDING THE CAUSE.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]SPEEDING THE CAUSE.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L17: isolated marker/symbol line :: 75</t>
@@ -641,7 +645,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>70</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -652,19 +656,19 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L55: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L57: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: iss, onâ€˜</t>
+          <t>L36: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: The words are " in every other case"—that is, in every •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
       <c r="M3" s="1" t="inlineStr"/>
       <c r="N3" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L55: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O3" s="1" t="inlineStr">
@@ -977,7 +981,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
